--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_FLEXIBLE.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_FLEXIBLE.xlsx
@@ -2352,11 +2352,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="34136288"/>
-        <c:axId val="26071558"/>
+        <c:axId val="2718100"/>
+        <c:axId val="49850096"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="34136288"/>
+        <c:axId val="2718100"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2390,7 +2390,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26071558"/>
+        <c:crossAx val="49850096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2402,7 +2402,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="26071558"/>
+        <c:axId val="49850096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2445,7 +2445,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34136288"/>
+        <c:crossAx val="2718100"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2968,11 +2968,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="99999803"/>
-        <c:axId val="21527706"/>
+        <c:axId val="71251514"/>
+        <c:axId val="5647901"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99999803"/>
+        <c:axId val="71251514"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3004,14 +3004,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21527706"/>
+        <c:crossAx val="5647901"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="21527706"/>
+        <c:axId val="5647901"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3085,7 +3085,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99999803"/>
+        <c:crossAx val="71251514"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="AW20" s="32" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="32" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2973,$B$3:$B$2973)</f>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AH22" s="22" t="n">
         <f aca="false">+S23/R23-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
@@ -5978,7 +5978,7 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="23" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="6" t="s">
         <v>27</v>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="S23" s="3" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="19"/>
       <c r="Y23" s="19"/>
@@ -6529,23 +6529,23 @@
       </c>
       <c r="AX29" s="42" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="42" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="42" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="42" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="42" t="n">
         <f aca="false">+AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="43"/>
       <c r="BD29" s="27"/>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="AH86" s="59" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI86" s="59"/>
       <c r="AJ86" s="59"/>
@@ -9705,7 +9705,7 @@
       <c r="AP86" s="59"/>
       <c r="AQ86" s="59" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="87" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15104,15 +15104,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="25" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="19" t="n">
         <f aca="false">+D248*(1+C249)</f>
-        <v>86.2114148401699</v>
+        <v>87.4474203710322</v>
       </c>
       <c r="F249" s="17" t="n">
         <v>46142</v>
@@ -15208,23 +15208,23 @@
       </c>
       <c r="T2" s="80" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="80" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="80" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="80" t="n">
         <f aca="false">+'Datos ICP (2)'!BA29</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="X2" s="80" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="H39" s="89" t="n">
         <f aca="false">+'Datos ICP (2)'!AH86</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I39" s="89"/>
       <c r="J39" s="89"/>
@@ -16347,7 +16347,7 @@
       <c r="P39" s="89"/>
       <c r="Q39" s="89" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_FLEXIBLE.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_FLEXIBLE.xlsx
@@ -2352,11 +2352,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="2718100"/>
-        <c:axId val="49850096"/>
+        <c:axId val="76401822"/>
+        <c:axId val="97859300"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="2718100"/>
+        <c:axId val="76401822"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2390,7 +2390,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49850096"/>
+        <c:crossAx val="97859300"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2402,7 +2402,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="49850096"/>
+        <c:axId val="97859300"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2445,7 +2445,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2718100"/>
+        <c:crossAx val="76401822"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2968,11 +2968,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="71251514"/>
-        <c:axId val="5647901"/>
+        <c:axId val="90490296"/>
+        <c:axId val="90991256"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="71251514"/>
+        <c:axId val="90490296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3004,14 +3004,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5647901"/>
+        <c:crossAx val="90991256"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="5647901"/>
+        <c:axId val="90991256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3085,7 +3085,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71251514"/>
+        <c:crossAx val="90490296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_FLEXIBLE.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_FLEXIBLE.xlsx
@@ -2352,11 +2352,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="76401822"/>
-        <c:axId val="97859300"/>
+        <c:axId val="66886035"/>
+        <c:axId val="47552522"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="76401822"/>
+        <c:axId val="66886035"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2390,7 +2390,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97859300"/>
+        <c:crossAx val="47552522"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2402,7 +2402,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="97859300"/>
+        <c:axId val="47552522"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2445,7 +2445,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76401822"/>
+        <c:crossAx val="66886035"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2968,11 +2968,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="90490296"/>
-        <c:axId val="90991256"/>
+        <c:axId val="55837372"/>
+        <c:axId val="2965830"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90490296"/>
+        <c:axId val="55837372"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3004,14 +3004,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90991256"/>
+        <c:crossAx val="2965830"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90991256"/>
+        <c:axId val="2965830"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3085,7 +3085,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90490296"/>
+        <c:crossAx val="55837372"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_FLEXIBLE.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_FLEXIBLE.xlsx
@@ -2352,11 +2352,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="66886035"/>
-        <c:axId val="47552522"/>
+        <c:axId val="97458261"/>
+        <c:axId val="5732983"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="66886035"/>
+        <c:axId val="97458261"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2390,7 +2390,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47552522"/>
+        <c:crossAx val="5732983"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2402,7 +2402,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="47552522"/>
+        <c:axId val="5732983"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2445,7 +2445,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66886035"/>
+        <c:crossAx val="97458261"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2968,11 +2968,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="55837372"/>
-        <c:axId val="2965830"/>
+        <c:axId val="32968073"/>
+        <c:axId val="12868724"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="55837372"/>
+        <c:axId val="32968073"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3004,14 +3004,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2965830"/>
+        <c:crossAx val="12868724"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="2965830"/>
+        <c:axId val="12868724"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3085,7 +3085,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55837372"/>
+        <c:crossAx val="32968073"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
